--- a/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
+++ b/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF67C075-1BF0-4BA4-BFB9-8BE7EE072914}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503B3E3F-F96B-4748-9A08-B8C46E8D7223}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="17505" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="17505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_per_kg" sheetId="15" r:id="rId1"/>
@@ -596,7 +596,7 @@
         <v>0.93402477368019154</v>
       </c>
       <c r="E3" s="4">
-        <v>6.7116426497261156E-2</v>
+        <v>7.159020601478655E-2</v>
       </c>
       <c r="F3" s="4">
         <v>6.0084848449833729E-2</v>
@@ -615,10 +615,10 @@
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>1.2812096743320678</v>
+        <v>1.2856834538495931</v>
       </c>
       <c r="L3" s="4">
-        <v>1.12798088049586</v>
+        <v>1.1316159298123001</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -633,31 +633,31 @@
         <v>0.78836444988837173</v>
       </c>
       <c r="D4" s="4">
-        <f>D2</f>
+        <f t="shared" ref="D4:J4" si="2">D2</f>
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <f>E2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <f>F2</f>
+        <f t="shared" si="2"/>
         <v>4.4663073022187867E-2</v>
       </c>
       <c r="G4" s="4">
-        <f>G2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f>H2</f>
+        <f t="shared" si="2"/>
         <v>1.0771319641479442</v>
       </c>
       <c r="I4" s="4">
-        <f>I2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J4" s="4">
-        <f>J2</f>
+        <f t="shared" si="2"/>
         <v>4.1427618661771248E-3</v>
       </c>
       <c r="K4" s="4">
@@ -684,35 +684,35 @@
         <v>0.14054270293045379</v>
       </c>
       <c r="E5" s="4">
-        <f>E3</f>
-        <v>6.7116426497261156E-2</v>
+        <f t="shared" ref="E5:J5" si="3">E3</f>
+        <v>7.159020601478655E-2</v>
       </c>
       <c r="F5" s="4">
-        <f>F3</f>
+        <f t="shared" si="3"/>
         <v>6.0084848449833729E-2</v>
       </c>
       <c r="G5" s="4">
-        <f>G3</f>
+        <f t="shared" si="3"/>
         <v>0.1373612714488579</v>
       </c>
       <c r="H5" s="4">
-        <f>H3</f>
+        <f t="shared" si="3"/>
         <v>1.2946870231381347E-3</v>
       </c>
       <c r="I5" s="4">
-        <f>I3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J5" s="4">
-        <f>J3</f>
+        <f t="shared" si="3"/>
         <v>8.1327667232785394E-2</v>
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>0.48772760358233008</v>
+        <v>0.49220138309985551</v>
       </c>
       <c r="L5" s="4">
-        <v>0.34204031191398099</v>
+        <v>0.34567536123042802</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +839,7 @@
       </c>
       <c r="E3" s="4">
         <f>climate_change_per_kg!E3*34</f>
-        <v>2.2819585009068795</v>
+        <v>2.4340670045027428</v>
       </c>
       <c r="F3" s="4">
         <f>climate_change_per_kg!F3*34</f>
@@ -863,11 +863,11 @@
       </c>
       <c r="K3" s="4">
         <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>43.561128927290305</v>
+        <v>43.713237430886167</v>
       </c>
       <c r="L3" s="4">
         <f>climate_change_per_kg!L3*34</f>
-        <v>38.351349936859236</v>
+        <v>38.474941613618199</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -937,7 +937,7 @@
       </c>
       <c r="E5" s="4">
         <f>climate_change_per_kg!E5*34</f>
-        <v>2.2819585009068795</v>
+        <v>2.4340670045027428</v>
       </c>
       <c r="F5" s="4">
         <f>climate_change_per_kg!F5*34</f>
@@ -961,11 +961,11 @@
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>16.582738521799225</v>
+        <v>16.734847025395087</v>
       </c>
       <c r="L5" s="4">
         <f>climate_change_per_kg!L5*34</f>
-        <v>11.629370605075353</v>
+        <v>11.752962281834552</v>
       </c>
     </row>
   </sheetData>
@@ -1107,31 +1107,31 @@
         <v>1.3230631140605693</v>
       </c>
       <c r="D4" s="4">
-        <f>D2</f>
+        <f t="shared" ref="D4:J4" si="2">D2</f>
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <f>E2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <f>F2</f>
+        <f t="shared" si="2"/>
         <v>6.1518196570525905E-3</v>
       </c>
       <c r="G4" s="4">
-        <f>G2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <f>H2</f>
+        <f t="shared" si="2"/>
         <v>0.15656587025320662</v>
       </c>
       <c r="I4" s="4">
-        <f>I2</f>
+        <f t="shared" si="2"/>
         <v>3.1237370934441819E-2</v>
       </c>
       <c r="J4" s="4">
-        <f>J2</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K4" s="4">
@@ -1155,27 +1155,27 @@
         <v>0.34480134971906312</v>
       </c>
       <c r="E5" s="4">
-        <f>E3</f>
+        <f t="shared" ref="E5:J5" si="3">E3</f>
         <v>1.7534231211380544</v>
       </c>
       <c r="F5" s="4">
-        <f>F3</f>
+        <f t="shared" si="3"/>
         <v>8.2752625114666644E-3</v>
       </c>
       <c r="G5" s="4">
-        <f>G3</f>
+        <f t="shared" si="3"/>
         <v>1.4012332202271671E-2</v>
       </c>
       <c r="H5" s="4">
-        <f>H3</f>
+        <f t="shared" si="3"/>
         <v>1.4292666501166196E-3</v>
       </c>
       <c r="I5" s="4">
-        <f>I3</f>
+        <f t="shared" si="3"/>
         <v>3.6477817859021072E-2</v>
       </c>
       <c r="J5" s="4">
-        <f>J3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K5" s="4">

--- a/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
+++ b/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503B3E3F-F96B-4748-9A08-B8C46E8D7223}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4107800-BD5A-4F9B-B1C7-EBF8A7720C82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="17505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_per_kg" sheetId="15" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
   <si>
     <t>Electricity</t>
   </si>
@@ -975,7 +975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4124028-3522-4FAA-99F9-57399465E007}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
@@ -988,9 +988,10 @@
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1022,11 @@
       <c r="K1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="L1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1030,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="4">
-        <v>0.70526625898807838</v>
+        <v>0.66966301383587246</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
@@ -1039,26 +1043,29 @@
         <v>0</v>
       </c>
       <c r="F2" s="4">
-        <v>6.1518196570525905E-3</v>
+        <v>5.6797478204711569E-3</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
       </c>
       <c r="H2" s="4">
-        <v>0.15656587025320662</v>
+        <v>0.10084034442435859</v>
       </c>
       <c r="I2" s="4">
-        <v>3.1237370934441819E-2</v>
+        <v>3.6329860958635281E-2</v>
       </c>
       <c r="J2" s="4">
         <v>0</v>
       </c>
       <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
-        <v>0.89922131983277942</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+        <v>0.81251296703933762</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.74123231010442647</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -1094,8 +1101,11 @@
         <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
         <v>1.9352147001162485</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="L3" s="4">
+        <v>1.9222716127473349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A5" si="1">A3+1</f>
         <v>2</v>
@@ -1104,7 +1114,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="4">
-        <v>1.3230631140605693</v>
+        <v>1.2562722534438617</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" ref="D4:J4" si="2">D2</f>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" si="2"/>
-        <v>6.1518196570525905E-3</v>
+        <v>5.6797478204711569E-3</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" si="2"/>
@@ -1124,11 +1134,11 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="2"/>
-        <v>0.15656587025320662</v>
+        <v>0.10084034442435859</v>
       </c>
       <c r="I4" s="4">
         <f t="shared" si="2"/>
-        <v>3.1237370934441819E-2</v>
+        <v>3.6329860958635281E-2</v>
       </c>
       <c r="J4" s="4">
         <f t="shared" si="2"/>
@@ -1136,10 +1146,13 @@
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>1.5170181749052705</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+        <v>1.3991222066473268</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.99399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1152,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="4">
-        <v>0.34480134971906312</v>
+        <v>0.40893343934519616</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" ref="E5:J5" si="3">E3</f>
@@ -1180,7 +1193,10 @@
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>2.1584191500799932</v>
+        <v>2.2225512397061262</v>
+      </c>
+      <c r="L5" s="4">
+        <v>2.0440955842108801</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917C59D4-EFB5-4206-AC6D-A6C0FCAFBA21}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
@@ -1203,9 +1219,10 @@
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1236,8 +1253,11 @@
       <c r="K1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="L1" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1246,7 +1266,7 @@
       </c>
       <c r="C2" s="4">
         <f>economics_per_kg!C2*44</f>
-        <v>31.031715395475448</v>
+        <v>29.465172608778389</v>
       </c>
       <c r="D2" s="4">
         <f>economics_per_kg!D2*44</f>
@@ -1258,7 +1278,7 @@
       </c>
       <c r="F2" s="4">
         <f>economics_per_kg!F2*44</f>
-        <v>0.27068006491031399</v>
+        <v>0.24990890410073091</v>
       </c>
       <c r="G2" s="4">
         <f>economics_per_kg!G2*44</f>
@@ -1266,11 +1286,11 @@
       </c>
       <c r="H2" s="4">
         <f>economics_per_kg!H2*44</f>
-        <v>6.888898291141091</v>
+        <v>4.4369751546717779</v>
       </c>
       <c r="I2" s="4">
         <f>economics_per_kg!I2*44</f>
-        <v>1.37444432111544</v>
+        <v>1.5985138821799523</v>
       </c>
       <c r="J2" s="4">
         <f>economics_per_kg!J2*44</f>
@@ -1278,10 +1298,14 @@
       </c>
       <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
-        <v>39.56573807264229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+        <v>35.750570549730845</v>
+      </c>
+      <c r="L2" s="4">
+        <f>economics_per_kg!L2*44</f>
+        <v>32.614221644594764</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -1325,8 +1349,12 @@
         <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
         <v>65.797299803952455</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="L3" s="4">
+        <f>economics_per_kg!L3*34</f>
+        <v>65.357234833409393</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A5" si="1">A3+1</f>
         <v>2</v>
@@ -1336,7 +1364,7 @@
       </c>
       <c r="C4" s="4">
         <f>economics_per_kg!C4*44</f>
-        <v>58.214777018665046</v>
+        <v>55.275979151529917</v>
       </c>
       <c r="D4" s="4">
         <f>economics_per_kg!D4*44</f>
@@ -1348,7 +1376,7 @@
       </c>
       <c r="F4" s="4">
         <f>economics_per_kg!F4*44</f>
-        <v>0.27068006491031399</v>
+        <v>0.24990890410073091</v>
       </c>
       <c r="G4" s="4">
         <f>economics_per_kg!G4*44</f>
@@ -1356,11 +1384,11 @@
       </c>
       <c r="H4" s="4">
         <f>economics_per_kg!H4*44</f>
-        <v>6.888898291141091</v>
+        <v>4.4369751546717779</v>
       </c>
       <c r="I4" s="4">
         <f>economics_per_kg!I4*44</f>
-        <v>1.37444432111544</v>
+        <v>1.5985138821799523</v>
       </c>
       <c r="J4" s="4">
         <f>economics_per_kg!J4*44</f>
@@ -1368,10 +1396,14 @@
       </c>
       <c r="K4" s="4">
         <f t="shared" si="0"/>
-        <v>66.748799695831892</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+        <v>61.561377092482374</v>
+      </c>
+      <c r="L4" s="4">
+        <f>economics_per_kg!L4*44</f>
+        <v>43.735999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1385,7 +1417,7 @@
       </c>
       <c r="D5" s="4">
         <f>economics_per_kg!D5*34</f>
-        <v>11.723245890448146</v>
+        <v>13.903736937736669</v>
       </c>
       <c r="E5" s="4">
         <f>economics_per_kg!E5*34</f>
@@ -1413,7 +1445,11 @@
       </c>
       <c r="K5" s="4">
         <f t="shared" si="0"/>
-        <v>73.386251102719783</v>
+        <v>75.566742150008309</v>
+      </c>
+      <c r="L5" s="4">
+        <f>economics_per_kg!L5*34</f>
+        <v>69.499249863169922</v>
       </c>
     </row>
   </sheetData>

--- a/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
+++ b/results/overall_nitrous_oxide_vs_hydrogen_peroxide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4107800-BD5A-4F9B-B1C7-EBF8A7720C82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB3A780-904F-4118-AE4D-4278AC1D0237}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="21600" windowHeight="8715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_per_kg" sheetId="15" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="14">
   <si>
     <t>Electricity</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>Impact 2050</t>
+  </si>
+  <si>
+    <t>Catalyst</t>
   </si>
 </sst>
 </file>
@@ -491,23 +494,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4941B293-21A4-490E-8B90-BF3EE8D79D2C}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -521,28 +525,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -559,29 +566,32 @@
         <v>0</v>
       </c>
       <c r="F2" s="4">
+        <v>4.5948930655782269E-3</v>
+      </c>
+      <c r="G2" s="4">
         <v>4.4663073022187867E-2</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
       <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <v>1.0771319641479442</v>
       </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
       <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
         <v>4.1427618661771248E-3</v>
       </c>
-      <c r="K2" s="4">
-        <f>SUM(C2:J2)</f>
-        <v>4.4215891660509534</v>
-      </c>
       <c r="L2" s="4">
+        <f>SUM(C2:K2)</f>
+        <v>4.4261840591165322</v>
+      </c>
+      <c r="M2" s="4">
         <v>3.03904716242775</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -599,31 +609,34 @@
         <v>7.159020601478655E-2</v>
       </c>
       <c r="F3" s="4">
+        <v>2.9785049369702079E-5</v>
+      </c>
+      <c r="G3" s="4">
         <v>6.0084848449833729E-2</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>0.1373612714488579</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>1.2946870231381347E-3</v>
       </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
       <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
         <v>8.1327667232785394E-2</v>
       </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>1.2856834538495931</v>
-      </c>
       <c r="L3" s="4">
+        <f>SUM(C3:K3)</f>
+        <v>1.2857132388989629</v>
+      </c>
+      <c r="M3" s="4">
         <v>1.1316159298123001</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A5" si="1">A3+1</f>
+        <f t="shared" ref="A4:A5" si="0">A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -633,44 +646,48 @@
         <v>0.78836444988837173</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:J4" si="2">D2</f>
+        <f t="shared" ref="D4:K4" si="1">D2</f>
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="2"/>
+        <f>F2</f>
+        <v>4.5948930655782269E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="1"/>
         <v>4.4663073022187867E-2</v>
       </c>
-      <c r="G4" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="H4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="1"/>
         <v>1.0771319641479442</v>
       </c>
-      <c r="I4" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="J4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" si="1"/>
         <v>4.1427618661771248E-3</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
+        <f>SUM(C4:K4)</f>
+        <v>1.9188971419902592</v>
+      </c>
+      <c r="M4" s="4">
+        <v>8.9747948381511497E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <f t="shared" si="0"/>
-        <v>1.914302248924681</v>
-      </c>
-      <c r="L4" s="4">
-        <v>8.9747948381511497E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -684,61 +701,90 @@
         <v>0.14054270293045379</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" ref="E5:J5" si="3">E3</f>
+        <f t="shared" ref="E5:K5" si="2">E3</f>
         <v>7.159020601478655E-2</v>
       </c>
       <c r="F5" s="4">
-        <f t="shared" si="3"/>
+        <f>F3</f>
+        <v>2.9785049369702079E-5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="2"/>
         <v>6.0084848449833729E-2</v>
       </c>
-      <c r="G5" s="4">
-        <f t="shared" si="3"/>
+      <c r="H5" s="4">
+        <f t="shared" si="2"/>
         <v>0.1373612714488579</v>
       </c>
-      <c r="H5" s="4">
-        <f t="shared" si="3"/>
+      <c r="I5" s="4">
+        <f t="shared" si="2"/>
         <v>1.2946870231381347E-3</v>
       </c>
-      <c r="I5" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="J5" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="2"/>
         <v>8.1327667232785394E-2</v>
       </c>
-      <c r="K5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.49220138309985551</v>
-      </c>
       <c r="L5" s="4">
+        <f>SUM(C5:K5)</f>
+        <v>0.49223116814922518</v>
+      </c>
+      <c r="M5" s="4">
         <v>0.34567536123042802</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L2:L5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEBA7EC0-0273-470A-BF1C-FDFDD2F0E9BF}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,28 +798,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -794,34 +843,38 @@
       </c>
       <c r="F2" s="4">
         <f>climate_change_per_kg!F2*44</f>
-        <v>1.9651752129762661</v>
+        <v>0.20217529488544198</v>
       </c>
       <c r="G2" s="4">
         <f>climate_change_per_kg!G2*44</f>
-        <v>0</v>
+        <v>1.9651752129762661</v>
       </c>
       <c r="H2" s="4">
         <f>climate_change_per_kg!H2*44</f>
-        <v>47.393806422509542</v>
+        <v>0</v>
       </c>
       <c r="I2" s="4">
         <f>climate_change_per_kg!I2*44</f>
-        <v>0</v>
+        <v>47.393806422509542</v>
       </c>
       <c r="J2" s="4">
         <f>climate_change_per_kg!J2*44</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <f>climate_change_per_kg!K2*44</f>
         <v>0.18228152211179349</v>
       </c>
-      <c r="K2" s="4">
-        <f>SUM(C2:J2)</f>
-        <v>194.54992330624196</v>
-      </c>
       <c r="L2" s="4">
-        <f>climate_change_per_kg!L2*44</f>
+        <f>SUM(C2:K2)</f>
+        <v>194.75209860112744</v>
+      </c>
+      <c r="M2" s="4">
+        <f>climate_change_per_kg!M2*44</f>
         <v>133.71807514682101</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -843,34 +896,38 @@
       </c>
       <c r="F3" s="4">
         <f>climate_change_per_kg!F3*34</f>
-        <v>2.0428848472943466</v>
+        <v>1.0126916785698707E-3</v>
       </c>
       <c r="G3" s="4">
         <f>climate_change_per_kg!G3*34</f>
-        <v>4.6702832292611687</v>
+        <v>2.0428848472943466</v>
       </c>
       <c r="H3" s="4">
         <f>climate_change_per_kg!H3*34</f>
-        <v>4.4019358786696577E-2</v>
+        <v>4.6702832292611687</v>
       </c>
       <c r="I3" s="4">
         <f>climate_change_per_kg!I3*34</f>
-        <v>0</v>
+        <v>4.4019358786696577E-2</v>
       </c>
       <c r="J3" s="4">
         <f>climate_change_per_kg!J3*34</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <f>climate_change_per_kg!K3*34</f>
         <v>2.7651406859147034</v>
       </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>43.713237430886167</v>
-      </c>
       <c r="L3" s="4">
-        <f>climate_change_per_kg!L3*34</f>
+        <f t="shared" ref="L3:L5" si="0">SUM(C3:K3)</f>
+        <v>43.714250122564735</v>
+      </c>
+      <c r="M3" s="4">
+        <f>climate_change_per_kg!M3*34</f>
         <v>38.474941613618199</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A5" si="1">A3+1</f>
         <v>2</v>
@@ -892,34 +949,38 @@
       </c>
       <c r="F4" s="4">
         <f>climate_change_per_kg!F4*44</f>
-        <v>1.9651752129762661</v>
+        <v>0.20217529488544198</v>
       </c>
       <c r="G4" s="4">
         <f>climate_change_per_kg!G4*44</f>
-        <v>0</v>
+        <v>1.9651752129762661</v>
       </c>
       <c r="H4" s="4">
         <f>climate_change_per_kg!H4*44</f>
-        <v>47.393806422509542</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4">
         <f>climate_change_per_kg!I4*44</f>
-        <v>0</v>
+        <v>47.393806422509542</v>
       </c>
       <c r="J4" s="4">
         <f>climate_change_per_kg!J4*44</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <f>climate_change_per_kg!K4*44</f>
         <v>0.18228152211179349</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>84.229298952685951</v>
-      </c>
-      <c r="L4" s="4">
-        <f>climate_change_per_kg!L4*44</f>
+        <v>84.431474247571401</v>
+      </c>
+      <c r="M4" s="4">
+        <f>climate_change_per_kg!M4*44</f>
         <v>3.9489097287865058</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -941,30 +1002,34 @@
       </c>
       <c r="F5" s="4">
         <f>climate_change_per_kg!F5*34</f>
-        <v>2.0428848472943466</v>
+        <v>1.0126916785698707E-3</v>
       </c>
       <c r="G5" s="4">
         <f>climate_change_per_kg!G5*34</f>
-        <v>4.6702832292611687</v>
+        <v>2.0428848472943466</v>
       </c>
       <c r="H5" s="4">
         <f>climate_change_per_kg!H5*34</f>
-        <v>4.4019358786696577E-2</v>
+        <v>4.6702832292611687</v>
       </c>
       <c r="I5" s="4">
         <f>climate_change_per_kg!I5*34</f>
-        <v>0</v>
+        <v>4.4019358786696577E-2</v>
       </c>
       <c r="J5" s="4">
         <f>climate_change_per_kg!J5*34</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="4">
+        <f>climate_change_per_kg!K5*34</f>
         <v>2.7651406859147034</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>16.734847025395087</v>
-      </c>
-      <c r="L5" s="4">
-        <f>climate_change_per_kg!L5*34</f>
+        <v>16.735859717073659</v>
+      </c>
+      <c r="M5" s="4">
+        <f>climate_change_per_kg!M5*34</f>
         <v>11.752962281834552</v>
       </c>
     </row>
@@ -975,23 +1040,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4124028-3522-4FAA-99F9-57399465E007}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1005,28 +1071,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1043,29 +1112,32 @@
         <v>0</v>
       </c>
       <c r="F2" s="4">
+        <v>5.2915975048236277E-3</v>
+      </c>
+      <c r="G2" s="4">
         <v>5.6797478204711569E-3</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
       <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
         <v>0.10084034442435859</v>
       </c>
-      <c r="I2" s="4">
+      <c r="J2" s="4">
         <v>3.6329860958635281E-2</v>
       </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
       <c r="K2" s="4">
-        <f>SUM(C2:J2)</f>
-        <v>0.81251296703933762</v>
+        <v>0</v>
       </c>
       <c r="L2" s="4">
+        <f>SUM(C2:K2)</f>
+        <v>0.81780456454416128</v>
+      </c>
+      <c r="M2" s="4">
         <v>0.74123231010442647</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -1083,31 +1155,34 @@
         <v>1.7534231211380544</v>
       </c>
       <c r="F3" s="4">
+        <v>1.702481917214814E-4</v>
+      </c>
+      <c r="G3" s="4">
         <v>8.2752625114666644E-3</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>1.4012332202271671E-2</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>1.4292666501166196E-3</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>3.6477817859021072E-2</v>
       </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
       <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>1.9352147001162485</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4">
+        <f>SUM(C3:K3)</f>
+        <v>1.9353849483079699</v>
+      </c>
+      <c r="M3" s="4">
         <v>1.9222716127473349</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
-        <f t="shared" ref="A4:A5" si="1">A3+1</f>
+        <f t="shared" ref="A4:A5" si="0">A3+1</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1117,44 +1192,48 @@
         <v>1.2562722534438617</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:J4" si="2">D2</f>
+        <f t="shared" ref="D4:K4" si="1">D2</f>
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="2"/>
+        <f>F2</f>
+        <v>5.2915975048236277E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="1"/>
         <v>5.6797478204711569E-3</v>
       </c>
-      <c r="G4" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="H4" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" si="1"/>
         <v>0.10084034442435859</v>
       </c>
-      <c r="I4" s="4">
-        <f t="shared" si="2"/>
+      <c r="J4" s="4">
+        <f t="shared" si="1"/>
         <v>3.6329860958635281E-2</v>
       </c>
-      <c r="J4" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="K4" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <f>SUM(C4:K4)</f>
+        <v>1.4044138041521503</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.99399999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <f t="shared" si="0"/>
-        <v>1.3991222066473268</v>
-      </c>
-      <c r="L4" s="4">
-        <v>0.99399999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1168,61 +1247,90 @@
         <v>0.40893343934519616</v>
       </c>
       <c r="E5" s="4">
-        <f t="shared" ref="E5:J5" si="3">E3</f>
+        <f t="shared" ref="E5:K5" si="2">E3</f>
         <v>1.7534231211380544</v>
       </c>
       <c r="F5" s="4">
-        <f t="shared" si="3"/>
+        <f>F3</f>
+        <v>1.702481917214814E-4</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="2"/>
         <v>8.2752625114666644E-3</v>
       </c>
-      <c r="G5" s="4">
-        <f t="shared" si="3"/>
+      <c r="H5" s="4">
+        <f t="shared" si="2"/>
         <v>1.4012332202271671E-2</v>
       </c>
-      <c r="H5" s="4">
-        <f t="shared" si="3"/>
+      <c r="I5" s="4">
+        <f t="shared" si="2"/>
         <v>1.4292666501166196E-3</v>
       </c>
-      <c r="I5" s="4">
-        <f t="shared" si="3"/>
+      <c r="J5" s="4">
+        <f t="shared" si="2"/>
         <v>3.6477817859021072E-2</v>
       </c>
-      <c r="J5" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
       <c r="K5" s="4">
-        <f t="shared" si="0"/>
-        <v>2.2225512397061262</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L5" s="4">
+        <f>SUM(C5:K5)</f>
+        <v>2.2227214878978478</v>
+      </c>
+      <c r="M5" s="4">
         <v>2.0440955842108801</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L2:L5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M5">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917C59D4-EFB5-4206-AC6D-A6C0FCAFBA21}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1236,28 +1344,31 @@
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1278,34 +1389,38 @@
       </c>
       <c r="F2" s="4">
         <f>economics_per_kg!F2*44</f>
-        <v>0.24990890410073091</v>
+        <v>0.23283029021223961</v>
       </c>
       <c r="G2" s="4">
         <f>economics_per_kg!G2*44</f>
-        <v>0</v>
+        <v>0.24990890410073091</v>
       </c>
       <c r="H2" s="4">
         <f>economics_per_kg!H2*44</f>
-        <v>4.4369751546717779</v>
+        <v>0</v>
       </c>
       <c r="I2" s="4">
         <f>economics_per_kg!I2*44</f>
-        <v>1.5985138821799523</v>
+        <v>4.4369751546717779</v>
       </c>
       <c r="J2" s="4">
         <f>economics_per_kg!J2*44</f>
-        <v>0</v>
+        <v>1.5985138821799523</v>
       </c>
       <c r="K2" s="4">
-        <f>SUM(C2:J2)</f>
-        <v>35.750570549730845</v>
+        <f>economics_per_kg!K2*44</f>
+        <v>0</v>
       </c>
       <c r="L2" s="4">
-        <f>economics_per_kg!L2*44</f>
+        <f>SUM(C2:K2)</f>
+        <v>35.983400839943087</v>
+      </c>
+      <c r="M2" s="4">
+        <f>economics_per_kg!M2*44</f>
         <v>32.614221644594764</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>A2+1</f>
         <v>1</v>
@@ -1327,34 +1442,38 @@
       </c>
       <c r="F3" s="4">
         <f>economics_per_kg!F3*34</f>
-        <v>0.28135892538986657</v>
+        <v>5.7884385185303679E-3</v>
       </c>
       <c r="G3" s="4">
         <f>economics_per_kg!G3*34</f>
-        <v>0.47641929487723678</v>
+        <v>0.28135892538986657</v>
       </c>
       <c r="H3" s="4">
         <f>economics_per_kg!H3*34</f>
-        <v>4.8595066103965065E-2</v>
+        <v>0.47641929487723678</v>
       </c>
       <c r="I3" s="4">
         <f>economics_per_kg!I3*34</f>
-        <v>1.2402458072067164</v>
+        <v>4.8595066103965065E-2</v>
       </c>
       <c r="J3" s="4">
         <f>economics_per_kg!J3*34</f>
-        <v>0</v>
+        <v>1.2402458072067164</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" ref="K3:K5" si="0">SUM(C3:J3)</f>
-        <v>65.797299803952455</v>
+        <f>economics_per_kg!K3*34</f>
+        <v>0</v>
       </c>
       <c r="L3" s="4">
-        <f>economics_per_kg!L3*34</f>
+        <f t="shared" ref="L3:L5" si="0">SUM(C3:K3)</f>
+        <v>65.803088242470992</v>
+      </c>
+      <c r="M3" s="4">
+        <f>economics_per_kg!M3*34</f>
         <v>65.357234833409393</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" ref="A4:A5" si="1">A3+1</f>
         <v>2</v>
@@ -1376,34 +1495,38 @@
       </c>
       <c r="F4" s="4">
         <f>economics_per_kg!F4*44</f>
-        <v>0.24990890410073091</v>
+        <v>0.23283029021223961</v>
       </c>
       <c r="G4" s="4">
         <f>economics_per_kg!G4*44</f>
-        <v>0</v>
+        <v>0.24990890410073091</v>
       </c>
       <c r="H4" s="4">
         <f>economics_per_kg!H4*44</f>
-        <v>4.4369751546717779</v>
+        <v>0</v>
       </c>
       <c r="I4" s="4">
         <f>economics_per_kg!I4*44</f>
-        <v>1.5985138821799523</v>
+        <v>4.4369751546717779</v>
       </c>
       <c r="J4" s="4">
         <f>economics_per_kg!J4*44</f>
-        <v>0</v>
+        <v>1.5985138821799523</v>
       </c>
       <c r="K4" s="4">
+        <f>economics_per_kg!K4*44</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>61.561377092482374</v>
-      </c>
-      <c r="L4" s="4">
-        <f>economics_per_kg!L4*44</f>
+        <v>61.794207382694616</v>
+      </c>
+      <c r="M4" s="4">
+        <f>economics_per_kg!M4*44</f>
         <v>43.735999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -1425,30 +1548,34 @@
       </c>
       <c r="F5" s="4">
         <f>economics_per_kg!F5*34</f>
-        <v>0.28135892538986657</v>
+        <v>5.7884385185303679E-3</v>
       </c>
       <c r="G5" s="4">
         <f>economics_per_kg!G5*34</f>
-        <v>0.47641929487723678</v>
+        <v>0.28135892538986657</v>
       </c>
       <c r="H5" s="4">
         <f>economics_per_kg!H5*34</f>
-        <v>4.8595066103965065E-2</v>
+        <v>0.47641929487723678</v>
       </c>
       <c r="I5" s="4">
         <f>economics_per_kg!I5*34</f>
-        <v>1.2402458072067164</v>
+        <v>4.8595066103965065E-2</v>
       </c>
       <c r="J5" s="4">
         <f>economics_per_kg!J5*34</f>
-        <v>0</v>
+        <v>1.2402458072067164</v>
       </c>
       <c r="K5" s="4">
+        <f>economics_per_kg!K5*34</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
         <f t="shared" si="0"/>
-        <v>75.566742150008309</v>
-      </c>
-      <c r="L5" s="4">
-        <f>economics_per_kg!L5*34</f>
+        <v>75.572530588526845</v>
+      </c>
+      <c r="M5" s="4">
+        <f>economics_per_kg!M5*34</f>
         <v>69.499249863169922</v>
       </c>
     </row>
